--- a/out/MLP-S4_repeat_5_000007.xlsx
+++ b/out/MLP-S4_repeat_5_000007.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.602580650042519</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.602580650042519</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.602580650042519</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>3.329251253104851</v>
+        <v>-1.602580650042519</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.3470245394981236</v>
+        <v>1.204705233669806</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.3470245394981236</v>
+        <v>-1.602580650042519</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.602580650042519</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.602580650042519</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.9470245394981236</v>
+        <v>1.204705233669806</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.002580650042519</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.002580650042519</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.602580650042519</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.9470245394981236</v>
+        <v>1.804705233669806</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.002580650042519</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.002580650042519</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.602580650042519</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.9470245394981236</v>
+        <v>1.804705233669806</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.002580650042519</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.002580650042519</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.9470245394981236</v>
+        <v>1.804705233669806</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.9470245394981236</v>
+        <v>1.804705233669806</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>3.329251253104851</v>
+        <v>1.804705233669806</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.3470245394981236</v>
+        <v>-1.002580650042519</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.3470245394981236</v>
+        <v>1.804705233669806</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.9470245394981236</v>
+        <v>1.804705233669806</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.002580650042519</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA28" t="n">
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.602580650042519</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.9470245394981236</v>
+        <v>1.204705233669806</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.9470245394981236</v>
+        <v>1.204705233669806</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.9470245394981236</v>
+        <v>1.804705233669806</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.9470245394981236</v>
+        <v>1.804705233669806</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.002580650042519</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.9470245394981236</v>
+        <v>1.204705233669806</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.9470245394981236</v>
+        <v>1.204705233669806</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>3.329251253104851</v>
+        <v>1.804705233669806</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>3.329251253104851</v>
+        <v>1.804705233669806</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>3.329251253104851</v>
+        <v>1.804705233669806</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,10 +31949,10 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>3.329251253104851</v>
+        <v>1.804705233669806</v>
       </c>
       <c r="JC39" t="n">
-        <v>-0.0003538824241188122</v>
+        <v>-0.0002376234232597053</v>
       </c>
     </row>
     <row r="40">
@@ -32733,7 +32733,7 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>4.079741699258714</v>
+        <v>2.739447047231245</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
@@ -32741,13 +32741,13 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>3.329251253104851</v>
+        <v>-1.602580650042519</v>
       </c>
       <c r="JC40" t="n">
-        <v>8.165789942918613</v>
+        <v>5.483128936768381</v>
       </c>
     </row>
     <row r="41">
@@ -33528,7 +33528,7 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.6117754666161401</v>
+        <v>0.4107923274812735</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
@@ -33539,10 +33539,10 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>3.329251253104851</v>
+        <v>1.204705233669806</v>
       </c>
       <c r="JC41" t="n">
-        <v>5.304123602363333</v>
+        <v>3.561589678233315</v>
       </c>
     </row>
     <row r="42">
@@ -34323,7 +34323,7 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.7649183921337491</v>
+        <v>0.5136240157902163</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
@@ -34334,10 +34334,10 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>3.329251253104851</v>
+        <v>1.204705233669806</v>
       </c>
       <c r="JC42" t="n">
-        <v>6.222282074225238</v>
+        <v>4.178110732595303</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>1.096506724898557</v>
+        <v>0.7362777534988119</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35129,10 +35129,10 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>3.329251253104851</v>
+        <v>1.804705233669806</v>
       </c>
       <c r="JC43" t="n">
-        <v>7.650809134797279</v>
+        <v>5.137331971150971</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>1.173045347884962</v>
+        <v>0.7876713545045746</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>3.329251253104851</v>
+        <v>1.804705233669806</v>
       </c>
       <c r="JC44" t="n">
-        <v>8.900474533913467</v>
+        <v>5.976451822207129</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>1.243191630517568</v>
+        <v>0.8347721355136229</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>2.729251253104852</v>
+        <v>1.804705233669806</v>
       </c>
       <c r="JC45" t="n">
-        <v>10.21390121139299</v>
+        <v>6.858385818424491</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.5610292610115669</v>
+        <v>0.3767171390184464</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>2.729251253104852</v>
+        <v>1.804705233669806</v>
       </c>
       <c r="JC46" t="n">
-        <v>10.0917350155928</v>
+        <v>6.776354124635788</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.2709514903614862</v>
+        <v>0.1819378028709106</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.602580650042519</v>
       </c>
       <c r="JC47" t="n">
-        <v>10.07216881170255</v>
+        <v>6.763215860876596</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.1291003184178782</v>
+        <v>0.0866879464347925</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>2.729251253104852</v>
+        <v>-1.602580650042519</v>
       </c>
       <c r="JC48" t="n">
-        <v>10.0592027851292</v>
+        <v>6.75450946703623</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.0382515238121213</v>
+        <v>0.02568503383966216</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.9470245394981236</v>
+        <v>1.204705233669806</v>
       </c>
       <c r="JC49" t="n">
-        <v>10.00646799810424</v>
+        <v>6.719099249238991</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.02530195658258603</v>
+        <v>0.01698969207672317</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.9470245394981236</v>
+        <v>1.204705233669806</v>
       </c>
       <c r="JC50" t="n">
-        <v>10.01880041476487</v>
+        <v>6.727380188341156</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.01294876912103231</v>
+        <v>0.008693163238125757</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.602580650042519</v>
       </c>
       <c r="JC51" t="n">
-        <v>10.01937823811419</v>
+        <v>6.727766541049704</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.006620850188763339</v>
+        <v>0.004444446647574286</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.602580650042519</v>
       </c>
       <c r="JC52" t="n">
-        <v>10.01966447082322</v>
+        <v>6.727957096821245</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.002485908262449208</v>
+        <v>0.001667715666974399</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.602580650042519</v>
       </c>
       <c r="JC53" t="n">
-        <v>10.01801016729367</v>
+        <v>6.72684471057711</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.001352959838567659</v>
+        <v>0.0009066316048707557</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.602580650042519</v>
       </c>
       <c r="JC54" t="n">
-        <v>10.01822803378639</v>
+        <v>6.726989326296707</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0006490627493095043</v>
+        <v>0.0004336909327081973</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.9470245394981236</v>
+        <v>1.204705233669806</v>
       </c>
       <c r="JC55" t="n">
-        <v>10.01817234077701</v>
+        <v>6.726950295326741</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.0003994055532658016</v>
+        <v>0.0002665716124120711</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.9470245394981236</v>
+        <v>1.804705233669806</v>
       </c>
       <c r="JC56" t="n">
-        <v>10.01832276784178</v>
+        <v>6.72704973193493</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.0002070500464420031</v>
+        <v>0.0001370529437329923</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.002580650042519</v>
       </c>
       <c r="JC57" t="n">
-        <v>10.01833624289172</v>
+        <v>6.727057153893298</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>9.79065924708733e-05</v>
+        <v>6.393742602417726e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>3.329251253104851</v>
+        <v>1.804705233669806</v>
       </c>
       <c r="JC58" t="n">
-        <v>10.01832487327649</v>
+        <v>6.727047856557099</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>6.02364652658983e-05</v>
+        <v>3.97701232216949e-05</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>3.329251253104851</v>
+        <v>-1.602580650042519</v>
       </c>
       <c r="JC59" t="n">
-        <v>10.01834867423505</v>
+        <v>6.727062429496506</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>2.530589321855379e-05</v>
+        <v>1.481539171982363e-05</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.3470245394981236</v>
+        <v>-1.002580650042519</v>
       </c>
       <c r="JC60" t="n">
-        <v>10.01833772649598</v>
+        <v>6.727053426918682</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>8.38179904731087e-06</v>
+        <v>4.264322417369065e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.3470245394981236</v>
+        <v>-1.602580650042519</v>
       </c>
       <c r="JC61" t="n">
-        <v>10.01832916366254</v>
+        <v>6.727045960341688</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>1.675769385467227e-06</v>
+        <v>-5.494870763551826e-07</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.602580650042519</v>
       </c>
       <c r="JC62" t="n">
-        <v>10.01832523921573</v>
+        <v>6.727041705163518</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>-2.093548687745288e-06</v>
+        <v>-3.062365791830193e-06</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.602580650042519</v>
       </c>
       <c r="JC63" t="n">
-        <v>10.01831922778914</v>
+        <v>6.727035982884487</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>-3.107779831880603e-06</v>
+        <v>-4.053889915940302e-06</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.9470245394981236</v>
+        <v>1.204705233669806</v>
       </c>
       <c r="JC64" t="n">
-        <v>10.01831413454701</v>
+        <v>6.727030913529118</v>
       </c>
     </row>
     <row r="65">
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>3.329251253104851</v>
+        <v>1.804705233669806</v>
       </c>
       <c r="JC65" t="n">
-        <v>10.01830976957304</v>
+        <v>6.727026548555149</v>
       </c>
     </row>
     <row r="66">
@@ -53414,10 +53414,10 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>3.329251253104851</v>
+        <v>1.804705233669806</v>
       </c>
       <c r="JC66" t="n">
-        <v>10.0183108608195</v>
+        <v>6.727027639801607</v>
       </c>
     </row>
     <row r="67">
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>3.329251253104851</v>
+        <v>-1.002580650042519</v>
       </c>
       <c r="JC67" t="n">
-        <v>10.01831017121236</v>
+        <v>6.72702695019447</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.3470245394981236</v>
+        <v>-1.002580650042519</v>
       </c>
       <c r="JC68" t="n">
-        <v>10.01831020152476</v>
+        <v>6.727026980506873</v>
       </c>
     </row>
     <row r="69">
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.3470245394981236</v>
+        <v>1.204705233669806</v>
       </c>
       <c r="JC69" t="n">
-        <v>10.01831001207225</v>
+        <v>6.727026791054363</v>
       </c>
     </row>
     <row r="70">
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.9470245394981236</v>
+        <v>1.804705233669806</v>
       </c>
       <c r="JC70" t="n">
-        <v>10.01831006511896</v>
+        <v>6.727026844101066</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.002580650042519</v>
       </c>
       <c r="JC71" t="n">
-        <v>10.01831011816566</v>
+        <v>6.727026897147768</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.602580650042519</v>
       </c>
       <c r="JC72" t="n">
-        <v>10.01831008027516</v>
+        <v>6.727026859257266</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.602580650042519</v>
       </c>
       <c r="JC73" t="n">
-        <v>10.01830995144745</v>
+        <v>6.727026730429559</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.602580650042519</v>
       </c>
       <c r="JC74" t="n">
-        <v>10.01830980746354</v>
+        <v>6.727026586445652</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.602580650042519</v>
       </c>
       <c r="JC75" t="n">
-        <v>10.01830964832343</v>
+        <v>6.727026427305544</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.602580650042519</v>
       </c>
       <c r="JC76" t="n">
-        <v>10.01830970137014</v>
+        <v>6.727026480352246</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.9470245394981236</v>
+        <v>1.804705233669806</v>
       </c>
       <c r="JC77" t="n">
-        <v>10.01830964832343</v>
+        <v>6.727026427305544</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.002580650042519</v>
       </c>
       <c r="JC78" t="n">
-        <v>10.01830964832343</v>
+        <v>6.727026427305544</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.9470245394981236</v>
+        <v>1.804705233669806</v>
       </c>
       <c r="JC79" t="n">
-        <v>10.01830946644902</v>
+        <v>6.727026245431134</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.9470245394981236</v>
+        <v>1.804705233669806</v>
       </c>
       <c r="JC80" t="n">
-        <v>10.01830963316723</v>
+        <v>6.727026412149343</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.002580650042519</v>
       </c>
       <c r="JC81" t="n">
-        <v>10.01830983019784</v>
+        <v>6.727026609179953</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.9470245394981236</v>
+        <v>1.804705233669806</v>
       </c>
       <c r="JC82" t="n">
-        <v>10.01830967105773</v>
+        <v>6.727026450039845</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.9470245394981236</v>
+        <v>1.804705233669806</v>
       </c>
       <c r="JC83" t="n">
-        <v>10.01830970894824</v>
+        <v>6.727026487930346</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.002580650042519</v>
       </c>
       <c r="JC84" t="n">
-        <v>10.01830990597885</v>
+        <v>6.727026684960957</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.602580650042519</v>
       </c>
       <c r="JC85" t="n">
-        <v>10.01830988324455</v>
+        <v>6.727026662226655</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.602580650042519</v>
       </c>
       <c r="JC86" t="n">
-        <v>10.01830973168254</v>
+        <v>6.727026510664648</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.9470245394981236</v>
+        <v>1.204705233669806</v>
       </c>
       <c r="JC87" t="n">
-        <v>10.01830965590153</v>
+        <v>6.727026434883644</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.9470245394981236</v>
+        <v>1.804705233669806</v>
       </c>
       <c r="JC88" t="n">
-        <v>10.01830975441684</v>
+        <v>6.727026533398949</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.9470245394981236</v>
+        <v>1.804705233669806</v>
       </c>
       <c r="JC89" t="n">
-        <v>10.01830976199494</v>
+        <v>6.727026540977049</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.002580650042519</v>
       </c>
       <c r="JC90" t="n">
-        <v>10.01831002722845</v>
+        <v>6.727026806210564</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.602580650042519</v>
       </c>
       <c r="JC91" t="n">
-        <v>10.01830973168254</v>
+        <v>6.727026510664648</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>3.329251253104851</v>
+        <v>1.204705233669806</v>
       </c>
       <c r="JC92" t="n">
-        <v>10.01830997418175</v>
+        <v>6.727026753163861</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.3470245394981236</v>
+        <v>-1.602580650042519</v>
       </c>
       <c r="JC93" t="n">
-        <v>10.01831005754086</v>
+        <v>6.727026836522965</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>3.329251253104851</v>
+        <v>1.804705233669806</v>
       </c>
       <c r="JC94" t="n">
-        <v>10.01830989082264</v>
+        <v>6.727026669804757</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.3470245394981236</v>
+        <v>-1.602580650042519</v>
       </c>
       <c r="JC95" t="n">
-        <v>10.01831008027516</v>
+        <v>6.727026859257266</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.3470245394981236</v>
+        <v>-1.602580650042519</v>
       </c>
       <c r="JC96" t="n">
-        <v>10.01830973168254</v>
+        <v>6.727026510664648</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.602580650042519</v>
       </c>
       <c r="JC97" t="n">
-        <v>10.01830952707383</v>
+        <v>6.727026306055937</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.602580650042519</v>
       </c>
       <c r="JC98" t="n">
-        <v>10.01830964074533</v>
+        <v>6.727026419727443</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.602580650042519</v>
       </c>
       <c r="JC99" t="n">
-        <v>10.01830965590153</v>
+        <v>6.727026434883644</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.602580650042519</v>
       </c>
       <c r="JC100" t="n">
-        <v>10.01830942098042</v>
+        <v>6.727026199962532</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.602580650042519</v>
       </c>
       <c r="JC101" t="n">
-        <v>10.01830948160522</v>
+        <v>6.727026260587334</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.9470245394981236</v>
+        <v>1.804705233669806</v>
       </c>
       <c r="JC102" t="n">
-        <v>10.01830935277752</v>
+        <v>6.727026131759628</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>3.329251253104851</v>
+        <v>1.804705233669806</v>
       </c>
       <c r="JC103" t="n">
-        <v>10.01830948918333</v>
+        <v>6.727026268165436</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.3470245394981236</v>
+        <v>1.804705233669806</v>
       </c>
       <c r="JC104" t="n">
-        <v>10.01830966347963</v>
+        <v>6.727026442461744</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.3470245394981236</v>
+        <v>-1.002580650042519</v>
       </c>
       <c r="JC105" t="n">
-        <v>10.01830980746354</v>
+        <v>6.727026586445652</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.9470245394981236</v>
+        <v>1.804705233669806</v>
       </c>
       <c r="JC106" t="n">
-        <v>10.01830964074533</v>
+        <v>6.727026419727443</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.602580650042519</v>
       </c>
       <c r="JC107" t="n">
-        <v>10.01830963316723</v>
+        <v>6.727026412149343</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.602580650042519</v>
       </c>
       <c r="JC108" t="n">
-        <v>10.01830934519942</v>
+        <v>6.727026124181528</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.9470245394981236</v>
+        <v>1.204705233669806</v>
       </c>
       <c r="JC109" t="n">
-        <v>10.01830936035562</v>
+        <v>6.727026139337728</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.9470245394981236</v>
+        <v>1.804705233669806</v>
       </c>
       <c r="JC110" t="n">
-        <v>10.01830958769863</v>
+        <v>6.72702636668074</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.9470245394981236</v>
+        <v>1.804705233669806</v>
       </c>
       <c r="JC111" t="n">
-        <v>10.01830957254243</v>
+        <v>6.72702635152454</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.002580650042519</v>
       </c>
       <c r="JC112" t="n">
-        <v>10.01830967863584</v>
+        <v>6.727026457617945</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.602580650042519</v>
       </c>
       <c r="JC113" t="n">
-        <v>10.01830940582422</v>
+        <v>6.727026184806331</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.9470245394981236</v>
+        <v>1.204705233669806</v>
       </c>
       <c r="JC114" t="n">
-        <v>10.01830950433953</v>
+        <v>6.727026283321636</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.9470245394981236</v>
+        <v>1.804705233669806</v>
       </c>
       <c r="JC115" t="n">
-        <v>10.01830965590153</v>
+        <v>6.727026434883644</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.9470245394981236</v>
+        <v>1.804705233669806</v>
       </c>
       <c r="JC116" t="n">
-        <v>10.01830967105773</v>
+        <v>6.727026450039845</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.9470245394981236</v>
+        <v>1.804705233669806</v>
       </c>
       <c r="JC117" t="n">
-        <v>10.01830964832343</v>
+        <v>6.727026427305544</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.9470245394981236</v>
+        <v>1.804705233669806</v>
       </c>
       <c r="JC118" t="n">
-        <v>10.01830973168254</v>
+        <v>6.727026510664648</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.602580650042519</v>
       </c>
       <c r="JC119" t="n">
-        <v>10.01830983019784</v>
+        <v>6.727026609179953</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.602580650042519</v>
       </c>
       <c r="JC120" t="n">
-        <v>10.01830966347963</v>
+        <v>6.727026442461744</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.9470245394981236</v>
+        <v>1.204705233669806</v>
       </c>
       <c r="JC121" t="n">
-        <v>10.01830964832343</v>
+        <v>6.727026427305544</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.602580650042519</v>
       </c>
       <c r="JC122" t="n">
-        <v>10.01830961801103</v>
+        <v>6.727026396993142</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.602580650042519</v>
       </c>
       <c r="JC123" t="n">
-        <v>10.01830960285483</v>
+        <v>6.727026381836941</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.602580650042519</v>
       </c>
       <c r="JC124" t="n">
-        <v>10.01830964074533</v>
+        <v>6.727026419727443</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.602580650042519</v>
       </c>
       <c r="JC125" t="n">
-        <v>10.01830965590153</v>
+        <v>6.727026434883644</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.602580650042519</v>
       </c>
       <c r="JC126" t="n">
-        <v>10.01830964832343</v>
+        <v>6.727026427305544</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP-S4_repeat_5_000007.xlsx
+++ b/out/MLP-S4_repeat_5_000007.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA4" t="n">
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.9470245394981236</v>
+        <v>0.3566176397962524</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>3.329251253104851</v>
+        <v>0.5566176397962525</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.3470245394981236</v>
+        <v>0.5566176397962526</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.3470245394981236</v>
+        <v>-0.2836739699415704</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.9470245394981236</v>
+        <v>0.5566176397962525</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>3.329251253104851</v>
+        <v>0.5566176397962525</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.3470245394981236</v>
+        <v>0.5566176397962526</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.3470245394981236</v>
+        <v>-0.2836739699415704</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.2836739699415704</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.9470245394981236</v>
+        <v>0.5566176397962526</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>3.329251253104851</v>
+        <v>1.396909249534076</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>3.329251253104851</v>
+        <v>2.237200859271899</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>3.329251253104851</v>
+        <v>2.237200859271899</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,10 +31949,10 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>3.329251253104851</v>
+        <v>2.237200859271899</v>
       </c>
       <c r="JC39" t="n">
-        <v>-0.0003538824241188122</v>
+        <v>-0.0002706047195544233</v>
       </c>
     </row>
     <row r="40">
@@ -32733,7 +32733,7 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>4.079741699258714</v>
+        <v>3.119672683256986</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
@@ -32744,10 +32744,10 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>3.329251253104851</v>
+        <v>2.237200859271899</v>
       </c>
       <c r="JC40" t="n">
-        <v>8.165789942918613</v>
+        <v>6.244167969034315</v>
       </c>
     </row>
     <row r="41">
@@ -33528,7 +33528,7 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.6117754666161401</v>
+        <v>0.4678088350142237</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
@@ -33539,10 +33539,10 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>3.329251253104851</v>
+        <v>2.237200859271899</v>
       </c>
       <c r="JC41" t="n">
-        <v>5.304123602363333</v>
+        <v>4.055925819860486</v>
       </c>
     </row>
     <row r="42">
@@ -34323,7 +34323,7 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.7649183921337491</v>
+        <v>0.5849133156594981</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
@@ -34334,10 +34334,10 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>3.329251253104851</v>
+        <v>2.237200859271899</v>
       </c>
       <c r="JC42" t="n">
-        <v>6.222282074225238</v>
+        <v>4.758017862097196</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>1.096506724898557</v>
+        <v>0.8384704641040128</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35129,10 +35129,10 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>3.329251253104851</v>
+        <v>2.237200859271899</v>
       </c>
       <c r="JC43" t="n">
-        <v>7.650809134797279</v>
+        <v>5.850375567118492</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>1.173045347884962</v>
+        <v>0.8969969644821033</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>3.329251253104851</v>
+        <v>2.237200859271899</v>
       </c>
       <c r="JC44" t="n">
-        <v>8.900474533913467</v>
+        <v>6.805962243481819</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>1.243191630517568</v>
+        <v>0.9506367219858297</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>2.729251253104852</v>
+        <v>2.237200859271899</v>
       </c>
       <c r="JC45" t="n">
-        <v>10.21390121139299</v>
+        <v>7.810305902655311</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.5610292610115669</v>
+        <v>0.4290046719540169</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>2.729251253104852</v>
+        <v>1.196909249534075</v>
       </c>
       <c r="JC46" t="n">
-        <v>10.0917350155928</v>
+        <v>7.716888549238423</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.2709514903614862</v>
+        <v>0.2071896482340246</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.9470245394981236</v>
+        <v>1.196909249534075</v>
       </c>
       <c r="JC47" t="n">
-        <v>10.07216881170255</v>
+        <v>7.70192677546893</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.1291003184178782</v>
+        <v>0.09871908605947417</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>2.729251253104852</v>
+        <v>0.3566176397962524</v>
       </c>
       <c r="JC48" t="n">
-        <v>10.0592027851292</v>
+        <v>7.692011988770401</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.0382515238121213</v>
+        <v>0.02925013978098177</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.9470245394981236</v>
+        <v>0.3566176397962524</v>
       </c>
       <c r="JC49" t="n">
-        <v>10.00646799810424</v>
+        <v>7.651686800697461</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.02530195658258603</v>
+        <v>0.01934787671225929</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC50" t="n">
-        <v>10.01880041476487</v>
+        <v>7.661117141641068</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.01294876912103231</v>
+        <v>0.00990047616721855</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC51" t="n">
-        <v>10.01937823811419</v>
+        <v>7.661557814459727</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.006620850188763339</v>
+        <v>0.005061530537837418</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC52" t="n">
-        <v>10.01966447082322</v>
+        <v>7.661775514161937</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.002485908262449208</v>
+        <v>0.001900079336549576</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC53" t="n">
-        <v>10.01801016729367</v>
+        <v>7.660509296435021</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.001352959838567659</v>
+        <v>0.001032857519391322</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC54" t="n">
-        <v>10.01822803378639</v>
+        <v>7.660674696380234</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0006490627493095043</v>
+        <v>0.0004948851389011886</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC55" t="n">
-        <v>10.01817234077701</v>
+        <v>7.66063092256492</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.0003994055532658016</v>
+        <v>0.0003049458619920377</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC56" t="n">
-        <v>10.01832276784178</v>
+        <v>7.660744900296945</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.0002070500464420031</v>
+        <v>0.0001566109577252159</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.9470245394981236</v>
+        <v>0.5566176397962523</v>
       </c>
       <c r="JC57" t="n">
-        <v>10.01833624289172</v>
+        <v>7.66075402626477</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>9.79065924708733e-05</v>
+        <v>7.392835733202904e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>3.329251253104851</v>
+        <v>1.396909249534076</v>
       </c>
       <c r="JC58" t="n">
-        <v>10.01832487327649</v>
+        <v>7.660744140831728</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>6.02364652658983e-05</v>
+        <v>4.488670873274575e-05</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>3.329251253104851</v>
+        <v>1.396909249534076</v>
       </c>
       <c r="JC59" t="n">
-        <v>10.01834867423505</v>
+        <v>7.660761231068211</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>2.530589321855379e-05</v>
+        <v>1.831222555273368e-05</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.3470245394981236</v>
+        <v>0.5566176397962523</v>
       </c>
       <c r="JC60" t="n">
-        <v>10.01833772649598</v>
+        <v>7.660751655884309</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>8.38179904731087e-06</v>
+        <v>5.293691574854516e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.3470245394981236</v>
+        <v>-0.2836739699415704</v>
       </c>
       <c r="JC61" t="n">
-        <v>10.01832916366254</v>
+        <v>7.660743915243203</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>1.675769385467227e-06</v>
+        <v>5.63141154556023e-07</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC62" t="n">
-        <v>10.01832523921573</v>
+        <v>7.66073974207161</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>-2.093548687745288e-06</v>
+        <v>-3.062365791830193e-06</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC63" t="n">
-        <v>10.01831922778914</v>
+        <v>7.660734019792579</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>-3.107779831880603e-06</v>
+        <v>-4.053889915940302e-06</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.9470245394981236</v>
+        <v>0.3566176397962523</v>
       </c>
       <c r="JC64" t="n">
-        <v>10.01831413454701</v>
+        <v>7.66072895043721</v>
       </c>
     </row>
     <row r="65">
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>3.329251253104851</v>
+        <v>1.396909249534075</v>
       </c>
       <c r="JC65" t="n">
-        <v>10.01830976957304</v>
+        <v>7.660724585463242</v>
       </c>
     </row>
     <row r="66">
@@ -53414,10 +53414,10 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>3.329251253104851</v>
+        <v>2.237200859271899</v>
       </c>
       <c r="JC66" t="n">
-        <v>10.0183108608195</v>
+        <v>7.660725676709698</v>
       </c>
     </row>
     <row r="67">
@@ -54209,10 +54209,10 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>3.329251253104851</v>
+        <v>1.396909249534075</v>
       </c>
       <c r="JC67" t="n">
-        <v>10.01831017121236</v>
+        <v>7.660724987102562</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.3470245394981236</v>
+        <v>0.5566176397962523</v>
       </c>
       <c r="JC68" t="n">
-        <v>10.01831020152476</v>
+        <v>7.660725017414965</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.3470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC69" t="n">
-        <v>10.01831001207225</v>
+        <v>7.660724827962454</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC70" t="n">
-        <v>10.01831006511896</v>
+        <v>7.660724881009158</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC71" t="n">
-        <v>10.01831011816566</v>
+        <v>7.660724934055859</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC72" t="n">
-        <v>10.01831008027516</v>
+        <v>7.660724896165358</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC73" t="n">
-        <v>10.01830995144745</v>
+        <v>7.660724767337652</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC74" t="n">
-        <v>10.01830980746354</v>
+        <v>7.660724623353744</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC75" t="n">
-        <v>10.01830964832343</v>
+        <v>7.660724464213636</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC76" t="n">
-        <v>10.01830970137014</v>
+        <v>7.66072451726034</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC77" t="n">
-        <v>10.01830964832343</v>
+        <v>7.660724464213636</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC78" t="n">
-        <v>10.01830964832343</v>
+        <v>7.660724464213636</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC79" t="n">
-        <v>10.01830946644902</v>
+        <v>7.660724282339227</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC80" t="n">
-        <v>10.01830963316723</v>
+        <v>7.660724449057436</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC81" t="n">
-        <v>10.01830983019784</v>
+        <v>7.660724646088045</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC82" t="n">
-        <v>10.01830967105773</v>
+        <v>7.660724486947937</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC83" t="n">
-        <v>10.01830970894824</v>
+        <v>7.660724524838439</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC84" t="n">
-        <v>10.01830990597885</v>
+        <v>7.66072472186905</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC85" t="n">
-        <v>10.01830988324455</v>
+        <v>7.660724699134748</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC86" t="n">
-        <v>10.01830973168254</v>
+        <v>7.660724547572739</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC87" t="n">
-        <v>10.01830965590153</v>
+        <v>7.660724471791736</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC88" t="n">
-        <v>10.01830975441684</v>
+        <v>7.660724570307041</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC89" t="n">
-        <v>10.01830976199494</v>
+        <v>7.660724577885142</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC90" t="n">
-        <v>10.01831002722845</v>
+        <v>7.660724843118655</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.9470245394981236</v>
+        <v>0.5566176397962523</v>
       </c>
       <c r="JC91" t="n">
-        <v>10.01830973168254</v>
+        <v>7.660724547572739</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>3.329251253104851</v>
+        <v>0.5566176397962523</v>
       </c>
       <c r="JC92" t="n">
-        <v>10.01830997418175</v>
+        <v>7.660724790071953</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.3470245394981236</v>
+        <v>1.396909249534076</v>
       </c>
       <c r="JC93" t="n">
-        <v>10.01831005754086</v>
+        <v>7.660724873431056</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>3.329251253104851</v>
+        <v>0.5566176397962525</v>
       </c>
       <c r="JC94" t="n">
-        <v>10.01830989082264</v>
+        <v>7.660724706712847</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.3470245394981236</v>
+        <v>0.5566176397962523</v>
       </c>
       <c r="JC95" t="n">
-        <v>10.01831008027516</v>
+        <v>7.660724896165358</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.3470245394981236</v>
+        <v>-0.2836739699415704</v>
       </c>
       <c r="JC96" t="n">
-        <v>10.01830973168254</v>
+        <v>7.660724547572739</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC97" t="n">
-        <v>10.01830952707383</v>
+        <v>7.660724342964029</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC98" t="n">
-        <v>10.01830964074533</v>
+        <v>7.660724456635535</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC99" t="n">
-        <v>10.01830965590153</v>
+        <v>7.660724471791736</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC100" t="n">
-        <v>10.01830942098042</v>
+        <v>7.660724236870625</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC101" t="n">
-        <v>10.01830948160522</v>
+        <v>7.660724297495427</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.9470245394981236</v>
+        <v>0.3566176397962524</v>
       </c>
       <c r="JC102" t="n">
-        <v>10.01830935277752</v>
+        <v>7.660724168667721</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>3.329251253104851</v>
+        <v>0.5566176397962523</v>
       </c>
       <c r="JC103" t="n">
-        <v>10.01830948918333</v>
+        <v>7.660724305073527</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.3470245394981236</v>
+        <v>0.5566176397962523</v>
       </c>
       <c r="JC104" t="n">
-        <v>10.01830966347963</v>
+        <v>7.660724479369836</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.3470245394981236</v>
+        <v>-0.2836739699415704</v>
       </c>
       <c r="JC105" t="n">
-        <v>10.01830980746354</v>
+        <v>7.660724623353744</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.2836739699415704</v>
       </c>
       <c r="JC106" t="n">
-        <v>10.01830964074533</v>
+        <v>7.660724456635535</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC107" t="n">
-        <v>10.01830963316723</v>
+        <v>7.660724449057436</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC108" t="n">
-        <v>10.01830934519942</v>
+        <v>7.66072416108962</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC109" t="n">
-        <v>10.01830936035562</v>
+        <v>7.66072417624582</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC110" t="n">
-        <v>10.01830958769863</v>
+        <v>7.660724403588834</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC111" t="n">
-        <v>10.01830957254243</v>
+        <v>7.660724388432631</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC112" t="n">
-        <v>10.01830967863584</v>
+        <v>7.660724494526038</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC113" t="n">
-        <v>10.01830940582422</v>
+        <v>7.660724221714422</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC114" t="n">
-        <v>10.01830950433953</v>
+        <v>7.660724320229728</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC115" t="n">
-        <v>10.01830965590153</v>
+        <v>7.660724471791736</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC116" t="n">
-        <v>10.01830967105773</v>
+        <v>7.660724486947937</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC117" t="n">
-        <v>10.01830964832343</v>
+        <v>7.660724464213636</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC118" t="n">
-        <v>10.01830973168254</v>
+        <v>7.660724547572739</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC119" t="n">
-        <v>10.01830983019784</v>
+        <v>7.660724646088045</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC120" t="n">
-        <v>10.01830966347963</v>
+        <v>7.660724479369836</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC121" t="n">
-        <v>10.01830964832343</v>
+        <v>7.660724464213636</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC122" t="n">
-        <v>10.01830961801103</v>
+        <v>7.660724433901233</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC123" t="n">
-        <v>10.01830960285483</v>
+        <v>7.660724418745033</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC124" t="n">
-        <v>10.01830964074533</v>
+        <v>7.660724456635535</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC125" t="n">
-        <v>10.01830965590153</v>
+        <v>7.660724471791736</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC126" t="n">
-        <v>10.01830964832343</v>
+        <v>7.660724464213636</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP-S4_repeat_5_000007.xlsx
+++ b/out/MLP-S4_repeat_5_000007.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>0.3895498514175415</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-1.28</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>0.4006393849849701</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.8599999999999997</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>0.3888835310935974</v>
       </c>
       <c r="JB4" t="n">
-        <v>0.3566176397962524</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0.5453402996063232</v>
       </c>
       <c r="JB5" t="n">
-        <v>0.5566176397962525</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>0.464872419834137</v>
       </c>
       <c r="JB6" t="n">
-        <v>0.5566176397962526</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>0.4185139238834381</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.2836739699415704</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>0.3938295841217041</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>0.4086648523807526</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>0.4092606008052826</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>0.4175524711608887</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>0.405486136674881</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>0.3920263946056366</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>0.4306297898292542</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.4836739699415704</v>
+        <v>0.16</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>0.4266798496246338</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.4836739699415704</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>0.4546603858470917</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.4836739699415704</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>0.4294863045215607</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.4836739699415704</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>0.4369735717773438</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.4836739699415704</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>0.419288843870163</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.4836739699415704</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>0.4492717385292053</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.4836739699415704</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0</v>
+        <v>0.4585895836353302</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.4836739699415704</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>0.4972757995128632</v>
       </c>
       <c r="JB22" t="n">
-        <v>0.5566176397962525</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0.5706567764282227</v>
       </c>
       <c r="JB23" t="n">
-        <v>0.5566176397962525</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>0.4982557594776154</v>
       </c>
       <c r="JB24" t="n">
-        <v>0.5566176397962526</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0</v>
+        <v>0.4716356992721558</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.2836739699415704</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>0.45957350730896</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.2836739699415704</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>0.4475084543228149</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.16</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0</v>
+        <v>0.428484708070755</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>0.4832347929477692</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.16</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>0.4783261120319366</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.16</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>0.4630525410175323</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.16</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>0.4485394358634949</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.16</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>0.4405364990234375</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.3</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>0.4525367319583893</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.3</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0</v>
+        <v>0.4555767774581909</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.5566176397962526</v>
+        <v>-0.16</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0.5520895719528198</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.396909249534076</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0.7276137471199036</v>
       </c>
       <c r="JB37" t="n">
-        <v>2.237200859271899</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0.6185608506202698</v>
       </c>
       <c r="JB38" t="n">
-        <v>2.237200859271899</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,13 +31946,13 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0.5861624479293823</v>
       </c>
       <c r="JB39" t="n">
-        <v>2.237200859271899</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC39" t="n">
-        <v>-0.0002706047195544233</v>
+        <v>-0.0001655819800505415</v>
       </c>
     </row>
     <row r="40">
@@ -32733,7 +32733,7 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>3.119672683256986</v>
+        <v>1.908915605419707</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
@@ -32741,13 +32741,13 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0.5775372385978699</v>
       </c>
       <c r="JB40" t="n">
-        <v>2.237200859271899</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC40" t="n">
-        <v>6.244167969034315</v>
+        <v>3.820782201421234</v>
       </c>
     </row>
     <row r="41">
@@ -33528,7 +33528,7 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.4678088350142237</v>
+        <v>0.2862504102768729</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
@@ -33536,13 +33536,13 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.5500870943069458</v>
       </c>
       <c r="JB41" t="n">
-        <v>2.237200859271899</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC41" t="n">
-        <v>4.055925819860486</v>
+        <v>2.481805283148065</v>
       </c>
     </row>
     <row r="42">
@@ -34323,7 +34323,7 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.5849133156594981</v>
+        <v>0.3579062094468367</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
@@ -34331,13 +34331,13 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.5041700005531311</v>
       </c>
       <c r="JB42" t="n">
-        <v>2.237200859271899</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC42" t="n">
-        <v>4.758017862097196</v>
+        <v>2.911412704952789</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0.8384704641040128</v>
+        <v>0.5130568539070393</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35126,13 +35126,13 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.6151804327964783</v>
       </c>
       <c r="JB43" t="n">
-        <v>2.237200859271899</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC43" t="n">
-        <v>5.850375567118492</v>
+        <v>3.579822185635244</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.8969969644821033</v>
+        <v>0.5488688594293036</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.6577486991882324</v>
       </c>
       <c r="JB44" t="n">
-        <v>2.237200859271899</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC44" t="n">
-        <v>6.805962243481819</v>
+        <v>4.164541999836108</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.9506367219858297</v>
+        <v>0.5816910990992846</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.7173343300819397</v>
       </c>
       <c r="JB45" t="n">
-        <v>2.237200859271899</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC45" t="n">
-        <v>7.810305902655311</v>
+        <v>4.779096175439199</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.4290046719540169</v>
+        <v>0.2625057084191442</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0.7848404049873352</v>
       </c>
       <c r="JB46" t="n">
-        <v>1.196909249534075</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC46" t="n">
-        <v>7.716888549238423</v>
+        <v>4.721934442921425</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.2071896482340246</v>
+        <v>0.1267789021009197</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0</v>
+        <v>0.4959006607532501</v>
       </c>
       <c r="JB47" t="n">
-        <v>1.196909249534075</v>
+        <v>-0.3</v>
       </c>
       <c r="JC47" t="n">
-        <v>7.70192677546893</v>
+        <v>4.712779365589396</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.09871908605947417</v>
+        <v>0.06040575950735491</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0.5812504887580872</v>
       </c>
       <c r="JB48" t="n">
-        <v>0.3566176397962524</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC48" t="n">
-        <v>7.692011988770401</v>
+        <v>4.706712529200177</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.02925013978098177</v>
+        <v>0.01789816837695915</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>0.4284294247627258</v>
       </c>
       <c r="JB49" t="n">
-        <v>0.3566176397962524</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC49" t="n">
-        <v>7.651686800697461</v>
+        <v>4.682037535803007</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.01934787671225929</v>
+        <v>0.01183757656008916</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>0.4260660409927368</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC50" t="n">
-        <v>7.661117141641068</v>
+        <v>4.687806569566344</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.00990047616721855</v>
+        <v>0.006056163523399848</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>0.3526161313056946</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC51" t="n">
-        <v>7.661557814459727</v>
+        <v>4.688074276883612</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.005061530537837418</v>
+        <v>0.003095519383377557</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>0.4009193181991577</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC52" t="n">
-        <v>7.661775514161937</v>
+        <v>4.68820554651627</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.001900079336549576</v>
+        <v>0.001160602772461799</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>0.3790374398231506</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC53" t="n">
-        <v>7.660509296435021</v>
+        <v>4.687428883703615</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.001032857519391322</v>
+        <v>0.0006302546024891238</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>0.3751197457313538</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC54" t="n">
-        <v>7.660674696380234</v>
+        <v>4.687528140811389</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0004948851389011886</v>
+        <v>0.0003009710309649564</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>0.3770231306552887</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC55" t="n">
-        <v>7.66063092256492</v>
+        <v>4.687499426584645</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.0003049458619920377</v>
+        <v>0.0001839193825475277</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>0.4155436158180237</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC56" t="n">
-        <v>7.660744900296945</v>
+        <v>4.687567135797627</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.0001566109577252159</v>
+        <v>9.381943911860337e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>0.3410890400409698</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.5566176397962523</v>
+        <v>0.16</v>
       </c>
       <c r="JC57" t="n">
-        <v>7.66075402626477</v>
+        <v>4.68757079099824</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>7.392835733202904e-05</v>
+        <v>4.295647027768853e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0.7180618047714233</v>
       </c>
       <c r="JB58" t="n">
-        <v>1.396909249534076</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC58" t="n">
-        <v>7.660744140831728</v>
+        <v>4.687562792321457</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>4.488670873274575e-05</v>
+        <v>2.569951306630508e-05</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0.5545238852500916</v>
       </c>
       <c r="JB59" t="n">
-        <v>1.396909249534076</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC59" t="n">
-        <v>7.660761231068211</v>
+        <v>4.687571494155336</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>1.831222555273368e-05</v>
+        <v>8.987335331640211e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>0.3350618183612823</v>
       </c>
       <c r="JB60" t="n">
-        <v>0.5566176397962523</v>
+        <v>0.16</v>
       </c>
       <c r="JC60" t="n">
-        <v>7.660751655884309</v>
+        <v>4.687563635373489</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>5.293691574854516e-06</v>
+        <v>1.176214944912711e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>0.3274122476577759</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.2836739699415704</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC61" t="n">
-        <v>7.660743915243203</v>
+        <v>4.687556854583018</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>5.63141154556023e-07</v>
+        <v>-1.662115307266386e-06</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>0.3502550423145294</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC62" t="n">
-        <v>7.66073974207161</v>
+        <v>4.687552434039168</v>
       </c>
     </row>
     <row r="63">
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>0.3222664892673492</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC63" t="n">
-        <v>7.660734019792579</v>
+        <v>4.687546855744045</v>
       </c>
     </row>
     <row r="64">
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>0.4007260203361511</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.3566176397962523</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC64" t="n">
-        <v>7.66072895043721</v>
+        <v>4.687541809122977</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>-3.735991635587426e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0.6095348596572876</v>
       </c>
       <c r="JB65" t="n">
-        <v>1.396909249534075</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC65" t="n">
-        <v>7.660724585463242</v>
+        <v>4.687542127403193</v>
       </c>
     </row>
     <row r="66">
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0.8952657580375671</v>
       </c>
       <c r="JB66" t="n">
-        <v>2.237200859271899</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC66" t="n">
-        <v>7.660725676709698</v>
+        <v>4.68754321864965</v>
       </c>
     </row>
     <row r="67">
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0.6246349811553955</v>
       </c>
       <c r="JB67" t="n">
-        <v>1.396909249534075</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC67" t="n">
-        <v>7.660724987102562</v>
+        <v>4.687542529042514</v>
       </c>
     </row>
     <row r="68">
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>0.3793875575065613</v>
       </c>
       <c r="JB68" t="n">
-        <v>0.5566176397962523</v>
+        <v>0.16</v>
       </c>
       <c r="JC68" t="n">
-        <v>7.660725017414965</v>
+        <v>4.687542559354916</v>
       </c>
     </row>
     <row r="69">
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>0.3356634378433228</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC69" t="n">
-        <v>7.660724827962454</v>
+        <v>4.687542369902406</v>
       </c>
     </row>
     <row r="70">
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>0.305558979511261</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC70" t="n">
-        <v>7.660724881009158</v>
+        <v>4.687542422949109</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>0.2631176710128784</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC71" t="n">
-        <v>7.660724934055859</v>
+        <v>4.687542475995811</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>0.2521009743213654</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC72" t="n">
-        <v>7.660724896165358</v>
+        <v>4.687542438105309</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>0.2475644052028656</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC73" t="n">
-        <v>7.660724767337652</v>
+        <v>4.687542309277602</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>0.2623922228813171</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC74" t="n">
-        <v>7.660724623353744</v>
+        <v>4.687542165293696</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>0.2868833839893341</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC75" t="n">
-        <v>7.660724464213636</v>
+        <v>4.687542006153588</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>0.3077223002910614</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC76" t="n">
-        <v>7.66072451726034</v>
+        <v>4.68754205920029</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>0.2949142158031464</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC77" t="n">
-        <v>7.660724464213636</v>
+        <v>4.687542006153588</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>0.3678549826145172</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.4836739699415704</v>
+        <v>0.16</v>
       </c>
       <c r="JC78" t="n">
-        <v>7.660724464213636</v>
+        <v>4.687542006153588</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>0.4357512891292572</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.4836739699415704</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC79" t="n">
-        <v>7.660724282339227</v>
+        <v>4.687541824279178</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>0.427552342414856</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.4836739699415704</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC80" t="n">
-        <v>7.660724449057436</v>
+        <v>4.687541990997386</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>0.3252788484096527</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.4836739699415704</v>
+        <v>0.16</v>
       </c>
       <c r="JC81" t="n">
-        <v>7.660724646088045</v>
+        <v>4.687542188027996</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>0.280744343996048</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.4836739699415704</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC82" t="n">
-        <v>7.660724486947937</v>
+        <v>4.687542028887888</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>0.3632075488567352</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC83" t="n">
-        <v>7.660724524838439</v>
+        <v>4.68754206677839</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>0.4045122563838959</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC84" t="n">
-        <v>7.66072472186905</v>
+        <v>4.687542263809</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>0.3215503990650177</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC85" t="n">
-        <v>7.660724699134748</v>
+        <v>4.687542241074699</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>0.276164710521698</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC86" t="n">
-        <v>7.660724547572739</v>
+        <v>4.687542089512691</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>0.3141761124134064</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC87" t="n">
-        <v>7.660724471791736</v>
+        <v>4.687542013731687</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0</v>
+        <v>0.3519066870212555</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC88" t="n">
-        <v>7.660724570307041</v>
+        <v>4.687542112246993</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>0.4451846778392792</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.4836739699415704</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC89" t="n">
-        <v>7.660724577885142</v>
+        <v>4.687542119825094</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>0.4346992075443268</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.4836739699415704</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC90" t="n">
-        <v>7.660724843118655</v>
+        <v>4.687542385058607</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>0.4194755256175995</v>
       </c>
       <c r="JB91" t="n">
-        <v>0.5566176397962523</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC91" t="n">
-        <v>7.660724547572739</v>
+        <v>4.687542089512691</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0.5197010040283203</v>
       </c>
       <c r="JB92" t="n">
-        <v>0.5566176397962523</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC92" t="n">
-        <v>7.660724790071953</v>
+        <v>4.687542332011904</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>0.4593747854232788</v>
       </c>
       <c r="JB93" t="n">
-        <v>1.396909249534076</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC93" t="n">
-        <v>7.660724873431056</v>
+        <v>4.687542415371008</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0.6256245374679565</v>
       </c>
       <c r="JB94" t="n">
-        <v>0.5566176397962525</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC94" t="n">
-        <v>7.660724706712847</v>
+        <v>4.6875422486528</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>0.4970445036888123</v>
       </c>
       <c r="JB95" t="n">
-        <v>0.5566176397962523</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC95" t="n">
-        <v>7.660724896165358</v>
+        <v>4.687542438105309</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>0.4017041623592377</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.2836739699415704</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC96" t="n">
-        <v>7.660724547572739</v>
+        <v>4.687542089512691</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>0.3584649860858917</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.3</v>
       </c>
       <c r="JC97" t="n">
-        <v>7.660724342964029</v>
+        <v>4.687541884903981</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>0.3640633523464203</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC98" t="n">
-        <v>7.660724456635535</v>
+        <v>4.687541998575486</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>0.3929094076156616</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC99" t="n">
-        <v>7.660724471791736</v>
+        <v>4.687542013731687</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>0.4251980483531952</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC100" t="n">
-        <v>7.660724236870625</v>
+        <v>4.687541778810576</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>0.3731061518192291</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.3</v>
       </c>
       <c r="JC101" t="n">
-        <v>7.660724297495427</v>
+        <v>4.687541839435378</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>0.3532502353191376</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.3566176397962524</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC102" t="n">
-        <v>7.660724168667721</v>
+        <v>4.687541710607671</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0.5052265524864197</v>
       </c>
       <c r="JB103" t="n">
-        <v>0.5566176397962523</v>
+        <v>-0.3</v>
       </c>
       <c r="JC103" t="n">
-        <v>7.660724305073527</v>
+        <v>4.687541847013479</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>0.4090460240840912</v>
       </c>
       <c r="JB104" t="n">
-        <v>0.5566176397962523</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC104" t="n">
-        <v>7.660724479369836</v>
+        <v>4.687542021309787</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>0.3803316354751587</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.2836739699415704</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC105" t="n">
-        <v>7.660724623353744</v>
+        <v>4.687542165293696</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>0.428648054599762</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.2836739699415704</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC106" t="n">
-        <v>7.660724456635535</v>
+        <v>4.687541998575486</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>0.4214565455913544</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.4836739699415704</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC107" t="n">
-        <v>7.660724449057436</v>
+        <v>4.687541990997386</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>0.3651248216629028</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC108" t="n">
-        <v>7.66072416108962</v>
+        <v>4.687541703029571</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>0.3819535970687866</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC109" t="n">
-        <v>7.66072417624582</v>
+        <v>4.687541718185773</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>0.3538396954536438</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC110" t="n">
-        <v>7.660724403588834</v>
+        <v>4.687541945528784</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>0.3821603059768677</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC111" t="n">
-        <v>7.660724388432631</v>
+        <v>4.687541930372583</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>0.3149368166923523</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC112" t="n">
-        <v>7.660724494526038</v>
+        <v>4.687542036465988</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>0.3031660616397858</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC113" t="n">
-        <v>7.660724221714422</v>
+        <v>4.687541763654375</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>0.3359382152557373</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC114" t="n">
-        <v>7.660724320229728</v>
+        <v>4.687541862169679</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>0.367311418056488</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC115" t="n">
-        <v>7.660724471791736</v>
+        <v>4.687542013731687</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>0.3716819584369659</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC116" t="n">
-        <v>7.660724486947937</v>
+        <v>4.687542028887888</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>0.4025779962539673</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.4836739699415704</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC117" t="n">
-        <v>7.660724464213636</v>
+        <v>4.687542006153588</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>0.4345451891422272</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.4836739699415704</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC118" t="n">
-        <v>7.660724547572739</v>
+        <v>4.687542089512691</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>0.3778176009654999</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.4836739699415704</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC119" t="n">
-        <v>7.660724646088045</v>
+        <v>4.687542188027996</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>0.3606842458248138</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC120" t="n">
-        <v>7.660724479369836</v>
+        <v>4.687542021309787</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>0.348484218120575</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.3999999999999999</v>
       </c>
       <c r="JC121" t="n">
-        <v>7.660724464213636</v>
+        <v>4.687542006153588</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>0.3353851735591888</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC122" t="n">
-        <v>7.660724433901233</v>
+        <v>4.687541975841185</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>0.3331027626991272</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC123" t="n">
-        <v>7.660724418745033</v>
+        <v>4.687541960684985</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>0.3109283447265625</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC124" t="n">
-        <v>7.660724456635535</v>
+        <v>4.687541998575486</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>0.3473666310310364</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.4836739699415704</v>
+        <v>0.1600000000000003</v>
       </c>
       <c r="JC125" t="n">
-        <v>7.660724471791736</v>
+        <v>4.687542013731687</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>0.4018309414386749</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.4836739699415704</v>
+        <v>0.4400000000000003</v>
       </c>
       <c r="JC126" t="n">
-        <v>7.660724464213636</v>
+        <v>4.687542006153588</v>
       </c>
     </row>
   </sheetData>
